--- a/results/canaliculi/543-2/measurements_euclidean.xlsx
+++ b/results/canaliculi/543-2/measurements_euclidean.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>euclidean</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>160.6667</v>
-      </c>
-      <c r="C6" t="n">
-        <v>143.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>95.48569999999999</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>12</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>27.4167</v>
+      </c>
+      <c r="C7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12.6308</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2595.7411</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2112.2865</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1867.7105</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>169.0441</v>
-      </c>
-      <c r="C7" t="n">
-        <v>164.7777</v>
-      </c>
-      <c r="D7" t="n">
-        <v>49.5201</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>86.3973</v>
+      </c>
+      <c r="C9" t="n">
+        <v>80.6426</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29.9186</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>12</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>27288.211</v>
+        <v>4112.6147</v>
       </c>
       <c r="D2" t="n">
-        <v>176.053</v>
+        <v>114.2393</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>429</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>104777.1896</v>
+        <v>4815.0706</v>
       </c>
       <c r="D3" t="n">
-        <v>244.2359</v>
+        <v>94.4131</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>16473.887</v>
+        <v>778.524</v>
       </c>
       <c r="D4" t="n">
-        <v>152.536</v>
+        <v>59.8865</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>174</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>24554.0887</v>
+        <v>755.9675999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>141.1155</v>
+        <v>32.8682</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>11213.9208</v>
+        <v>969.8915</v>
       </c>
       <c r="D6" t="n">
-        <v>109.9404</v>
+        <v>74.607</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>17806.2768</v>
+        <v>2396.719</v>
       </c>
       <c r="D7" t="n">
-        <v>153.5024</v>
+        <v>77.3135</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4186.0025</v>
+        <v>860.2102</v>
       </c>
       <c r="D8" t="n">
-        <v>89.0639</v>
+        <v>78.2009</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
-        <v>37474.8421</v>
+        <v>4112.2472</v>
       </c>
       <c r="D9" t="n">
-        <v>192.1787</v>
+        <v>114.2291</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>19128.953</v>
+        <v>1827.854</v>
       </c>
       <c r="D10" t="n">
-        <v>178.7753</v>
+        <v>83.0843</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>35703.9149</v>
+        <v>1268.9991</v>
       </c>
       <c r="D11" t="n">
-        <v>227.4135</v>
+        <v>63.45</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -815,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>16944.5548</v>
+        <v>2911.5374</v>
       </c>
       <c r="D12" t="n">
-        <v>128.3678</v>
+        <v>97.05119999999999</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -837,13 +888,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>48481.4961</v>
+        <v>6339.2576</v>
       </c>
       <c r="D13" t="n">
-        <v>235.3471</v>
+        <v>147.4246</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
